--- a/zy70942/discrepancy_WB2026050001.xlsx
+++ b/zy70942/discrepancy_WB2026050001.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,82 @@
       <c r="H2" s="5" t="inlineStr">
         <is>
           <t>计算路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>晚点扣罚</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DELAY_002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>晚点扣罚-一般</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'delay_hours': 12.0, 'threshold_hours': 12.0, 'freight': 500.0, 'declared_value': 50000.0}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BATCH_20260527_001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>{'source': 'delay_calculation', 'rule_version': 'v1.0', 'formula': 'percentage: 10.0'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>晚点扣罚</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DELAY_001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>晚点扣罚-轻微</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'delay_hours': 12.0, 'threshold_hours': 4.0, 'freight': 500.0, 'declared_value': 50000.0}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BATCH_20260527_001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{'source': 'delay_calculation', 'rule_version': 'v1.0', 'formula': 'percentage: 5.0'}</t>
         </is>
       </c>
     </row>
